--- a/기안파일/Lease_Renewal_Proposal.xlsx
+++ b/기안파일/Lease_Renewal_Proposal.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\바이브 코딩\project 0. 부동산 자산관리 앱\기안파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\OneDrive\Desktop\바이브 코딩\project 0. 부동산 자산관리 앱\기안파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1385EB0-2B06-4FBB-B59E-92AD1FCABC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C77D88-3F35-4148-A20E-D3BDB2829815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="임대갱신품의서" sheetId="1" r:id="rId1"/>
     <sheet name="비교표" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="156">
   <si>
     <t>C&amp;W Approval</t>
   </si>
@@ -189,9 +202,6 @@
 임대시작일</t>
   </si>
   <si>
-    <t>1-Apr-26</t>
-  </si>
-  <si>
     <t>Budgeted income per month
 월 예산 수입 (월 보증금 수익+임대료+관리비)</t>
   </si>
@@ -204,9 +214,6 @@
   <si>
     <t>Annual income of last lease
 기존 연 수익(연 보증금 수익+임대료+관리비)</t>
-  </si>
-  <si>
-    <t>226,127,070</t>
   </si>
   <si>
     <t>Annual income of current lease
@@ -554,7 +561,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,6 +611,13 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -660,34 +677,46 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -695,27 +724,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1019,789 +1047,794 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="8" width="9.5" customWidth="1"/>
     <col min="9" max="9" width="14.9140625" customWidth="1"/>
     <col min="10" max="10" width="12.25" customWidth="1"/>
     <col min="11" max="12" width="9.5" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" customHeight="1">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:12" ht="18" customHeight="1">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:12" ht="18" customHeight="1">
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="18" customHeight="1"/>
     <row r="5" spans="1:12" ht="18" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
     </row>
     <row r="6" spans="1:12" ht="28" customHeight="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="7" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="10" t="s">
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="10"/>
+      <c r="L6" s="13"/>
     </row>
     <row r="7" spans="1:12" ht="29" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="4" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="7" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="4" t="s">
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="4"/>
+      <c r="L7" s="7"/>
     </row>
     <row r="8" spans="1:12" ht="30.5" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="4" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="7" t="s">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="4" t="s">
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="4"/>
+      <c r="L8" s="7"/>
     </row>
     <row r="9" spans="1:12" ht="18" customHeight="1"/>
     <row r="10" spans="1:12" ht="18" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12" ht="25" customHeight="1">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="2" t="s">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="1" t="s">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
     </row>
     <row r="12" spans="1:12" ht="18" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1" t="s">
+      <c r="A12" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="1" t="s">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="1" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="2" t="s">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="1" t="s">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
     </row>
     <row r="14" spans="1:12" ht="28" customHeight="1">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="1" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="2" t="s">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="1" t="s">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
     </row>
     <row r="15" spans="1:12" ht="29" customHeight="1">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="2" t="s">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="1" t="s">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
     </row>
     <row r="16" spans="1:12" ht="18" customHeight="1"/>
-    <row r="17" spans="1:12" ht="18" customHeight="1">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:13" ht="18" customHeight="1">
+      <c r="A17" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-    </row>
-    <row r="18" spans="1:12" ht="26.5" customHeight="1">
-      <c r="A18" s="2" t="s">
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+    </row>
+    <row r="18" spans="1:13" ht="26.5" customHeight="1">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="1" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="2" t="s">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="1" t="s">
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-    </row>
-    <row r="19" spans="1:12" ht="29" customHeight="1">
-      <c r="A19" s="2" t="s">
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="1:13" ht="29" customHeight="1">
+      <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="2" t="s">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="1" t="s">
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-    </row>
-    <row r="20" spans="1:12" ht="35.5" customHeight="1">
-      <c r="A20" s="7" t="s">
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="20">
+        <f>926100*12+780040*12+30000000*0.03</f>
+        <v>21373680</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="35.5" customHeight="1">
+      <c r="A20" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="9" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="2" t="s">
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="1" t="s">
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-    </row>
-    <row r="21" spans="1:12" ht="25" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:13" ht="25" customHeight="1">
+      <c r="A21" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="1" t="s">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="2" t="s">
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="1" t="s">
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-    </row>
-    <row r="22" spans="1:12" ht="29.5" customHeight="1">
-      <c r="A22" s="2" t="s">
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:13" ht="29.5" customHeight="1">
+      <c r="A22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="1" t="s">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="18">
+        <v>46113</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:13" ht="18" customHeight="1"/>
+    <row r="24" spans="1:13" ht="18" customHeight="1">
+      <c r="A24" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-    </row>
-    <row r="23" spans="1:12" ht="18" customHeight="1"/>
-    <row r="24" spans="1:12" ht="18" customHeight="1">
-      <c r="A24" s="5" t="s">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+    </row>
+    <row r="25" spans="1:13" ht="29" customHeight="1">
+      <c r="A25" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-    </row>
-    <row r="25" spans="1:12" ht="29" customHeight="1">
-      <c r="A25" s="2" t="s">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="19">
+        <v>226127070</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="1" t="s">
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="2" t="s">
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+    </row>
+    <row r="26" spans="1:13" ht="34.5" customHeight="1">
+      <c r="A26" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="1" t="s">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-    </row>
-    <row r="26" spans="1:12" ht="34.5" customHeight="1">
-      <c r="A26" s="6" t="s">
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+    </row>
+    <row r="27" spans="1:13" ht="32.5" customHeight="1">
+      <c r="A27" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="4" t="s">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" spans="1:12" ht="32.5" customHeight="1">
-      <c r="A27" s="6" t="s">
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+    </row>
+    <row r="28" spans="1:13" ht="18" customHeight="1"/>
+    <row r="29" spans="1:13" ht="18" customHeight="1">
+      <c r="A29" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="4" t="s">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+    </row>
+    <row r="30" spans="1:13" ht="26.5" customHeight="1">
+      <c r="A30" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-    </row>
-    <row r="28" spans="1:12" ht="18" customHeight="1"/>
-    <row r="29" spans="1:12" ht="18" customHeight="1">
-      <c r="A29" s="5" t="s">
+      <c r="B30" s="9"/>
+      <c r="C30" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-    </row>
-    <row r="30" spans="1:12" ht="26.5" customHeight="1">
-      <c r="A30" s="6" t="s">
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6" t="s">
+      <c r="L30" s="9"/>
+    </row>
+    <row r="31" spans="1:13" ht="18" customHeight="1">
+      <c r="A31" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="L30" s="6"/>
-    </row>
-    <row r="31" spans="1:12" ht="18" customHeight="1">
-      <c r="A31" s="6" t="s">
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="1" t="s">
+      <c r="L31" s="7"/>
+    </row>
+    <row r="32" spans="1:13" ht="18" customHeight="1">
+      <c r="A32" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="4" t="s">
+      <c r="B32" s="9"/>
+      <c r="C32" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="L31" s="4"/>
-    </row>
-    <row r="32" spans="1:12" ht="18" customHeight="1">
-      <c r="A32" s="6" t="s">
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="1" t="s">
+      <c r="L32" s="7"/>
+    </row>
+    <row r="33" spans="1:12" ht="18" customHeight="1">
+      <c r="A33" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="4" t="s">
+      <c r="B33" s="9"/>
+      <c r="C33" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="L32" s="4"/>
-    </row>
-    <row r="33" spans="1:12" ht="18" customHeight="1">
-      <c r="A33" s="6" t="s">
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="1" t="s">
+      <c r="L33" s="7"/>
+    </row>
+    <row r="34" spans="1:12" ht="18" customHeight="1">
+      <c r="A34" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="4" t="s">
+      <c r="B34" s="9"/>
+      <c r="C34" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="L33" s="4"/>
-    </row>
-    <row r="34" spans="1:12" ht="18" customHeight="1">
-      <c r="A34" s="6" t="s">
+      <c r="D34" s="6"/>
+      <c r="E34" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="1" t="s">
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="4" t="s">
+      <c r="L34" s="7"/>
+    </row>
+    <row r="35" spans="1:12" ht="18" customHeight="1">
+      <c r="A35" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4" t="s">
+      <c r="B35" s="9"/>
+      <c r="C35" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="L34" s="4"/>
-    </row>
-    <row r="35" spans="1:12" ht="18" customHeight="1">
-      <c r="A35" s="6" t="s">
+      <c r="D35" s="6"/>
+      <c r="E35" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="1" t="s">
+      <c r="F35" s="6"/>
+      <c r="G35" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1" t="s">
+      <c r="H35" s="6"/>
+      <c r="I35" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1" t="s">
+      <c r="J35" s="6"/>
+      <c r="K35" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="L35" s="1"/>
+      <c r="L35" s="6"/>
     </row>
     <row r="36" spans="1:12" ht="18" customHeight="1"/>
     <row r="37" spans="1:12" ht="18" customHeight="1">
-      <c r="A37" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
+      <c r="A37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
     </row>
     <row r="38" spans="1:12" ht="18" customHeight="1">
-      <c r="A38" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
+      <c r="A38" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
     </row>
     <row r="39" spans="1:12" ht="18" customHeight="1">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
     </row>
     <row r="40" spans="1:12" ht="18" customHeight="1">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
-      <c r="L40" s="13"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
     </row>
     <row r="41" spans="1:12" ht="18" customHeight="1">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="13"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
     </row>
     <row r="42" spans="1:12" ht="18" customHeight="1">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
-      <c r="L42" s="13"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="13"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
     </row>
     <row r="44" spans="1:12" ht="18" customHeight="1">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
-      <c r="L44" s="13"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
     </row>
     <row r="45" spans="1:12" ht="18" customHeight="1">
-      <c r="A45" s="13"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
     </row>
     <row r="46" spans="1:12" ht="18" customHeight="1">
-      <c r="A46" s="13"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
-      <c r="L46" s="13"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
     </row>
     <row r="47" spans="1:12" ht="18" customHeight="1">
-      <c r="A47" s="13"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
-      <c r="L47" s="13"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
     </row>
     <row r="48" spans="1:12" ht="18" customHeight="1">
-      <c r="A48" s="13"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
     </row>
     <row r="49" ht="18" customHeight="1"/>
     <row r="50" ht="18" customHeight="1"/>
@@ -1834,56 +1867,35 @@
     <row r="77" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="111">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="A38:L48"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="G26:L26"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="J25:L25"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D7:G7"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="J19:L19"/>
@@ -1902,49 +1914,70 @@
     <mergeCell ref="G18:I18"/>
     <mergeCell ref="J20:L20"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="G35:H35"/>
     <mergeCell ref="A24:L24"/>
-    <mergeCell ref="I35:J35"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="D21:F21"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
     <mergeCell ref="J15:L15"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A17:L17"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="G27:L27"/>
+    <mergeCell ref="A38:L48"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
     <mergeCell ref="K30:L30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="E34:J34"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="A37:L37"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="J25:L25"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1958,552 +1991,492 @@
   <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:12" ht="21">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" ht="38.5" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" spans="1:12" ht="38.5" customHeight="1">
-      <c r="A2" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="3" t="s">
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="6" t="s">
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="6" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="6" t="s">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="4" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="6" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="4" t="s">
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="6" t="s">
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="4" t="s">
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+    </row>
+    <row r="9" spans="1:12" ht="80" customHeight="1">
+      <c r="A9" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4" t="s">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" spans="1:12" ht="80" customHeight="1">
-      <c r="A9" s="6" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="4" t="s">
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="6" t="s">
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="4" t="s">
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="3" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="3" t="s">
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3" t="s">
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3" t="s">
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="1" t="s">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="6" t="s">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="1" t="s">
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1" t="s">
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="6" t="s">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="1" t="s">
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1" t="s">
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1" t="s">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" s="6" t="s">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="1" t="s">
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" s="3" t="s">
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="9" t="s">
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9" t="s">
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="C20" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9" t="s">
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="C20" s="6" t="s">
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="C21" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="1" t="s">
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:12">
-      <c r="C21" s="6" t="s">
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="1" t="s">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+    </row>
+    <row r="24" spans="1:12" ht="30.5" customHeight="1">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="A23" s="3" t="s">
+      <c r="D24" s="15"/>
+      <c r="E24" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="1:12" ht="30.5" customHeight="1">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="15"/>
+      <c r="G24" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3" t="s">
+      <c r="H24" s="15"/>
+      <c r="I24" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3" t="s">
+      <c r="J24" s="15"/>
+      <c r="K24" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3" t="s">
+      <c r="L24" s="15"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="1:12">
-      <c r="A25" s="6" t="s">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="4" t="s">
+      <c r="F25" s="7"/>
+      <c r="G25" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
+      <c r="H25" s="7"/>
+      <c r="I25" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
+      <c r="J25" s="7"/>
+      <c r="K25" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4" t="s">
+      <c r="L25" s="7"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4" t="s">
+      <c r="B26" s="9"/>
+      <c r="C26" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L25" s="4"/>
-    </row>
-    <row r="26" spans="1:12">
-      <c r="A26" s="6" t="s">
+      <c r="D26" s="7"/>
+      <c r="E26" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="4" t="s">
+      <c r="F26" s="7"/>
+      <c r="G26" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4" t="s">
+      <c r="H26" s="7"/>
+      <c r="I26" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4" t="s">
+      <c r="J26" s="7"/>
+      <c r="K26" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4" t="s">
+      <c r="L26" s="7"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" spans="1:12">
-      <c r="A27" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="A12:L12"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="G18:I18"/>
     <mergeCell ref="A27:L27"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D7:F7"/>
@@ -2520,10 +2493,70 @@
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="A12:L12"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="G15:I15"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J17:L17"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
